--- a/academias/Ciencias Sociales - Estadisticos 20241.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20241.xlsx
@@ -1041,25 +1041,25 @@
         <v>40</v>
       </c>
       <c r="E17">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
         <v>9</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1073,25 +1073,25 @@
         <v>40</v>
       </c>
       <c r="E18">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
         <v>9</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1102,25 +1102,25 @@
         <v>324</v>
       </c>
       <c r="E19">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F19">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19" s="1">
-        <v>89.2</v>
+        <v>89.5</v>
       </c>
       <c r="H19" s="1">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="I19" s="2">
         <v>7.7</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1188,25 +1188,25 @@
         <v>41</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F2">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>4.9</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1223,25 +1223,25 @@
         <v>25</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1255,25 +1255,25 @@
         <v>66</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F4">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>6.1</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J4">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1290,25 +1290,25 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1322,25 +1322,25 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1357,25 +1357,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J7">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1389,25 +1389,25 @@
         <v>36</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F8">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J8">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1424,25 +1424,25 @@
         <v>28</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1459,25 +1459,25 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>91.2</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J10">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1491,25 +1491,25 @@
         <v>62</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F11">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>88.7</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>11.3</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J11">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1596,25 +1596,25 @@
         <v>18</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F14">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J14">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1631,25 +1631,25 @@
         <v>23</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F15">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>95.7</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>4.3</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J15">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1663,25 +1663,25 @@
         <v>89</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F16">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>38.2</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>61.8</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J16">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1698,25 +1698,25 @@
         <v>40</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F17">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J17">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1730,25 +1730,25 @@
         <v>40</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F18">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J18">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1759,25 +1759,25 @@
         <v>324</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="F19">
-        <v>324</v>
+        <v>66</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>20.4</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J19">
-        <v>324</v>
+        <v>54</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
   </sheetData>
@@ -1845,19 +1845,19 @@
         <v>41</v>
       </c>
       <c r="E2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>92.7</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>7.3</v>
+        <v>4.9</v>
       </c>
       <c r="I2" s="2">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1880,19 +1880,19 @@
         <v>25</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1912,16 +1912,16 @@
         <v>66</v>
       </c>
       <c r="E4">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>92.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="H4" s="1">
-        <v>7.6</v>
+        <v>3</v>
       </c>
       <c r="I4" s="2">
         <v>8.6</v>
@@ -1959,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1991,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2026,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2058,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>14.3</v>
       </c>
       <c r="I9" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2116,19 +2116,19 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>94.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="H10" s="1">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I10" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2148,16 +2148,16 @@
         <v>62</v>
       </c>
       <c r="E11">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>90.3</v>
+        <v>88.7</v>
       </c>
       <c r="H11" s="1">
-        <v>9.699999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="I11" s="2">
         <v>8</v>
@@ -2265,7 +2265,7 @@
         <v>16.7</v>
       </c>
       <c r="I14" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2288,19 +2288,19 @@
         <v>23</v>
       </c>
       <c r="E15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>95.7</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2320,19 +2320,19 @@
         <v>89</v>
       </c>
       <c r="E16">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G16" s="1">
-        <v>74.2</v>
+        <v>75.3</v>
       </c>
       <c r="H16" s="1">
-        <v>25.8</v>
+        <v>24.7</v>
       </c>
       <c r="I16" s="2">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2355,25 +2355,25 @@
         <v>40</v>
       </c>
       <c r="E17">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2387,25 +2387,25 @@
         <v>40</v>
       </c>
       <c r="E18">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2416,25 +2416,25 @@
         <v>324</v>
       </c>
       <c r="E19">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F19">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G19" s="1">
-        <v>89.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>10.8</v>
+        <v>9.6</v>
       </c>
       <c r="I19" s="2">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Ciencias Sociales - Estadisticos 20241.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20241.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="32">
   <si>
     <t>Docente</t>
   </si>
@@ -54,6 +54,9 @@
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
+    <t>Diaz Rodriguez Aurelio</t>
+  </si>
+  <si>
     <t>Miguel Lopez Yadira</t>
   </si>
   <si>
@@ -78,10 +81,13 @@
     <t>Totales Generales</t>
   </si>
   <si>
+    <t>5ASV</t>
+  </si>
+  <si>
     <t>5ALCM</t>
   </si>
   <si>
-    <t>5ASV</t>
+    <t>5APM</t>
   </si>
   <si>
     <t>5BEM</t>
@@ -91,9 +97,6 @@
   </si>
   <si>
     <t>5AEM</t>
-  </si>
-  <si>
-    <t>5APM</t>
   </si>
   <si>
     <t>5AEV</t>
@@ -472,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -522,28 +525,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>92.7</v>
+        <v>92</v>
       </c>
       <c r="H2" s="1">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="I2" s="2">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -557,10 +560,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>25</v>
@@ -589,28 +589,31 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
       <c r="D4">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E4">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>92.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="H4" s="1">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="I4" s="2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -624,28 +627,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="I5" s="2">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -659,25 +662,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I6" s="2">
-        <v>7.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -691,16 +694,16 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -712,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -726,13 +729,13 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -744,7 +747,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -758,28 +761,28 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -793,28 +796,25 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -825,28 +825,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
       </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
       <c r="D11">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="E11">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>90.3</v>
+        <v>85.7</v>
       </c>
       <c r="H11" s="1">
-        <v>9.699999999999999</v>
+        <v>14.3</v>
       </c>
       <c r="I11" s="2">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -860,28 +863,25 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D12">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E12">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>55</v>
+        <v>85.7</v>
       </c>
       <c r="H12" s="1">
-        <v>45</v>
+        <v>14.3</v>
       </c>
       <c r="I12" s="2">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -892,31 +892,31 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
       </c>
       <c r="D13">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E13">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>64.3</v>
+        <v>55</v>
       </c>
       <c r="H13" s="1">
-        <v>35.7</v>
+        <v>45</v>
       </c>
       <c r="I13" s="2">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -927,31 +927,31 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
       </c>
       <c r="D14">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G14" s="1">
-        <v>83.3</v>
+        <v>64.3</v>
       </c>
       <c r="H14" s="1">
-        <v>16.7</v>
+        <v>35.7</v>
       </c>
       <c r="I14" s="2">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -962,31 +962,31 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
         <v>29</v>
       </c>
       <c r="D15">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E15">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>95.7</v>
+        <v>83.3</v>
       </c>
       <c r="H15" s="1">
-        <v>4.3</v>
+        <v>16.7</v>
       </c>
       <c r="I15" s="2">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -997,28 +997,31 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
         <v>18</v>
       </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
       <c r="D16">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="E16">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="F16">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>74.2</v>
+        <v>95.7</v>
       </c>
       <c r="H16" s="1">
-        <v>25.8</v>
+        <v>4.3</v>
       </c>
       <c r="I16" s="2">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1032,28 +1035,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D17">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="E17">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G17" s="1">
-        <v>100</v>
+        <v>74.2</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>25.8</v>
       </c>
       <c r="I17" s="2">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1064,10 +1064,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
       </c>
       <c r="D18">
         <v>40</v>
@@ -1095,31 +1098,63 @@
       </c>
     </row>
     <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
       <c r="B19" t="s">
         <v>19</v>
       </c>
       <c r="D19">
+        <v>40</v>
+      </c>
+      <c r="E19">
+        <v>40</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>100</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>9</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20">
         <v>324</v>
       </c>
-      <c r="E19">
+      <c r="E20">
         <v>290</v>
       </c>
-      <c r="F19">
+      <c r="F20">
         <v>34</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G20" s="1">
         <v>89.5</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H20" s="1">
         <v>10.5</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I20" s="2">
         <v>7.7</v>
       </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1130,7 +1165,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="30.7109375" customWidth="1"/>
@@ -1179,28 +1214,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>95.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1214,66 +1249,66 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>25</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
       <c r="D4">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E4">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>93.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>6.1</v>
+        <v>4.9</v>
       </c>
       <c r="I4" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1281,28 +1316,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E5">
         <v>31</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I5" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1316,25 +1351,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I6" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1348,16 +1383,16 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1369,7 +1404,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>9.4</v>
+        <v>7.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1383,13 +1418,13 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1401,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>9.4</v>
+        <v>7.5</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1415,28 +1450,28 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1450,28 +1485,25 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E10">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>91.2</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1482,25 +1514,28 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
       </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
       <c r="D11">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="E11">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>88.7</v>
+        <v>85.7</v>
       </c>
       <c r="H11" s="1">
-        <v>11.3</v>
+        <v>14.3</v>
       </c>
       <c r="I11" s="2">
         <v>7.6</v>
@@ -1517,171 +1552,171 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D12">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J12">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
       </c>
       <c r="D13">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F13">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="J13">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
       </c>
       <c r="D14">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E14">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="H14" s="1">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="I14" s="2">
-        <v>7.7</v>
+        <v>6.3</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
         <v>29</v>
       </c>
       <c r="D15">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E15">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>95.7</v>
+        <v>83.3</v>
       </c>
       <c r="H15" s="1">
-        <v>4.3</v>
+        <v>16.7</v>
       </c>
       <c r="I15" s="2">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>4.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
         <v>18</v>
       </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
       <c r="D16">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="E16">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F16">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>38.2</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>61.8</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="J16">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>58.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1689,28 +1724,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D17">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="E17">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G17" s="1">
-        <v>100</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>23.6</v>
       </c>
       <c r="I17" s="2">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1721,10 +1753,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
       </c>
       <c r="D18">
         <v>40</v>
@@ -1752,32 +1787,64 @@
       </c>
     </row>
     <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
       <c r="B19" t="s">
         <v>19</v>
       </c>
       <c r="D19">
+        <v>40</v>
+      </c>
+      <c r="E19">
+        <v>40</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>100</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20">
         <v>324</v>
       </c>
-      <c r="E19">
-        <v>258</v>
-      </c>
-      <c r="F19">
-        <v>66</v>
-      </c>
-      <c r="G19" s="1">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="H19" s="1">
-        <v>20.4</v>
-      </c>
-      <c r="I19" s="2">
-        <v>6.7</v>
-      </c>
-      <c r="J19">
-        <v>54</v>
-      </c>
-      <c r="K19" s="1">
-        <v>16.7</v>
+      <c r="E20">
+        <v>294</v>
+      </c>
+      <c r="F20">
+        <v>30</v>
+      </c>
+      <c r="G20" s="1">
+        <v>90.7</v>
+      </c>
+      <c r="H20" s="1">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I20" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1787,7 +1854,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="30.7109375" customWidth="1"/>
@@ -1836,28 +1903,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>95.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1871,10 +1938,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>25</v>
@@ -1892,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1903,28 +1967,31 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
       <c r="D4">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E4">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="F4">
         <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>97</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="I4" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1938,28 +2005,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E5">
         <v>31</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I5" s="2">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1973,25 +2040,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I6" s="2">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2005,16 +2072,16 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -2026,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>9.4</v>
+        <v>7.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2040,13 +2107,13 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -2058,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>9.4</v>
+        <v>7.9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2072,28 +2139,28 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2107,28 +2174,25 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E10">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>91.2</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2139,28 +2203,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
       </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
       <c r="D11">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="E11">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>88.7</v>
+        <v>85.7</v>
       </c>
       <c r="H11" s="1">
-        <v>11.3</v>
+        <v>14.3</v>
       </c>
       <c r="I11" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2174,28 +2241,25 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D12">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E12">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>55</v>
+        <v>85.7</v>
       </c>
       <c r="H12" s="1">
-        <v>45</v>
+        <v>14.3</v>
       </c>
       <c r="I12" s="2">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2206,31 +2270,31 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
       </c>
       <c r="D13">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E13">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13" s="1">
-        <v>64.3</v>
+        <v>45</v>
       </c>
       <c r="H13" s="1">
-        <v>35.7</v>
+        <v>55</v>
       </c>
       <c r="I13" s="2">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2241,31 +2305,31 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
       </c>
       <c r="D14">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="H14" s="1">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="I14" s="2">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2276,31 +2340,31 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
         <v>29</v>
       </c>
       <c r="D15">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E15">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="I15" s="2">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2311,28 +2375,31 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
         <v>18</v>
       </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
       <c r="D16">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="E16">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="F16">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>75.3</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>24.7</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>6.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2346,28 +2413,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D17">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="E17">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G17" s="1">
-        <v>100</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>23.6</v>
       </c>
       <c r="I17" s="2">
-        <v>9.4</v>
+        <v>6.9</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2378,10 +2442,13 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
       </c>
       <c r="D18">
         <v>40</v>
@@ -2409,31 +2476,63 @@
       </c>
     </row>
     <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
       <c r="B19" t="s">
         <v>19</v>
       </c>
       <c r="D19">
+        <v>40</v>
+      </c>
+      <c r="E19">
+        <v>40</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>100</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20">
         <v>324</v>
       </c>
-      <c r="E19">
-        <v>293</v>
-      </c>
-      <c r="F19">
-        <v>31</v>
-      </c>
-      <c r="G19" s="1">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="H19" s="1">
-        <v>9.6</v>
-      </c>
-      <c r="I19" s="2">
+      <c r="E20">
+        <v>294</v>
+      </c>
+      <c r="F20">
+        <v>30</v>
+      </c>
+      <c r="G20" s="1">
+        <v>90.7</v>
+      </c>
+      <c r="H20" s="1">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I20" s="2">
         <v>7.9</v>
       </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Ciencias Sociales - Estadisticos 20241.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20241.xlsx
@@ -531,28 +531,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E2">
         <v>23</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>92</v>
+        <v>79.3</v>
       </c>
       <c r="H2" s="1">
-        <v>8</v>
+        <v>20.7</v>
       </c>
       <c r="I2" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K2" s="1">
-        <v>0</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -563,28 +563,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E3">
         <v>23</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>92</v>
+        <v>79.3</v>
       </c>
       <c r="H3" s="1">
-        <v>8</v>
+        <v>20.7</v>
       </c>
       <c r="I3" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -834,28 +834,28 @@
         <v>26</v>
       </c>
       <c r="D11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E11">
         <v>24</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>85.7</v>
+        <v>82.8</v>
       </c>
       <c r="H11" s="1">
-        <v>14.3</v>
+        <v>17.2</v>
       </c>
       <c r="I11" s="2">
         <v>7.4</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -866,28 +866,28 @@
         <v>19</v>
       </c>
       <c r="D12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E12">
         <v>24</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>85.7</v>
+        <v>82.8</v>
       </c>
       <c r="H12" s="1">
-        <v>14.3</v>
+        <v>17.2</v>
       </c>
       <c r="I12" s="2">
         <v>7.4</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -901,28 +901,28 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13">
         <v>11</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>55</v>
+        <v>52.4</v>
       </c>
       <c r="H13" s="1">
-        <v>45</v>
+        <v>47.6</v>
       </c>
       <c r="I13" s="2">
         <v>5.5</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1006,28 +1006,28 @@
         <v>30</v>
       </c>
       <c r="D16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E16">
         <v>22</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>95.7</v>
+        <v>91.7</v>
       </c>
       <c r="H16" s="1">
-        <v>4.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I16" s="2">
         <v>7.6</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1038,28 +1038,28 @@
         <v>19</v>
       </c>
       <c r="D17">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E17">
         <v>66</v>
       </c>
       <c r="F17">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G17" s="1">
-        <v>74.2</v>
+        <v>72.5</v>
       </c>
       <c r="H17" s="1">
-        <v>25.8</v>
+        <v>27.5</v>
       </c>
       <c r="I17" s="2">
         <v>6.6</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" s="1">
-        <v>0</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1073,28 +1073,28 @@
         <v>31</v>
       </c>
       <c r="D18">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E18">
         <v>40</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G18" s="1">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="I18" s="2">
         <v>9</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K18" s="1">
-        <v>0</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1105,28 +1105,28 @@
         <v>19</v>
       </c>
       <c r="D19">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E19">
         <v>40</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="I19" s="2">
         <v>9</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K19" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1134,28 +1134,28 @@
         <v>20</v>
       </c>
       <c r="D20">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E20">
         <v>290</v>
       </c>
       <c r="F20">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="G20" s="1">
-        <v>89.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>10.5</v>
+        <v>13.4</v>
       </c>
       <c r="I20" s="2">
         <v>7.7</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K20" s="1">
-        <v>0</v>
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
@@ -1220,28 +1220,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E2">
         <v>25</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="I2" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K2" s="1">
-        <v>0</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1252,28 +1252,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E3">
         <v>25</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="I3" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1302,7 +1302,7 @@
         <v>4.9</v>
       </c>
       <c r="I4" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1325,19 +1325,19 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>91.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="I5" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1357,19 +1357,19 @@
         <v>75</v>
       </c>
       <c r="E6">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>93.3</v>
+        <v>94.7</v>
       </c>
       <c r="H6" s="1">
-        <v>6.7</v>
+        <v>5.3</v>
       </c>
       <c r="I6" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1523,28 +1523,28 @@
         <v>26</v>
       </c>
       <c r="D11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E11">
         <v>24</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>85.7</v>
+        <v>82.8</v>
       </c>
       <c r="H11" s="1">
-        <v>14.3</v>
+        <v>17.2</v>
       </c>
       <c r="I11" s="2">
         <v>7.6</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1555,28 +1555,28 @@
         <v>19</v>
       </c>
       <c r="D12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E12">
         <v>24</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>85.7</v>
+        <v>82.8</v>
       </c>
       <c r="H12" s="1">
-        <v>14.3</v>
+        <v>17.2</v>
       </c>
       <c r="I12" s="2">
         <v>7.6</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1590,28 +1590,28 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13">
         <v>9</v>
       </c>
       <c r="F13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1">
-        <v>45</v>
+        <v>42.9</v>
       </c>
       <c r="H13" s="1">
-        <v>55</v>
+        <v>57.1</v>
       </c>
       <c r="I13" s="2">
         <v>5.8</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1695,28 +1695,28 @@
         <v>30</v>
       </c>
       <c r="D16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E16">
         <v>23</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I16" s="2">
         <v>8.4</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1727,28 +1727,28 @@
         <v>19</v>
       </c>
       <c r="D17">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E17">
         <v>68</v>
       </c>
       <c r="F17">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G17" s="1">
-        <v>76.40000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="H17" s="1">
-        <v>23.6</v>
+        <v>25.3</v>
       </c>
       <c r="I17" s="2">
         <v>7</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" s="1">
-        <v>0</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1762,28 +1762,28 @@
         <v>31</v>
       </c>
       <c r="D18">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E18">
         <v>40</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G18" s="1">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="I18" s="2">
         <v>9.4</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K18" s="1">
-        <v>0</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1794,28 +1794,28 @@
         <v>19</v>
       </c>
       <c r="D19">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E19">
         <v>40</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="I19" s="2">
         <v>9.4</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K19" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1823,28 +1823,28 @@
         <v>20</v>
       </c>
       <c r="D20">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E20">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F20">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G20" s="1">
-        <v>90.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>9.300000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="I20" s="2">
         <v>7.8</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K20" s="1">
-        <v>0</v>
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
@@ -1909,28 +1909,28 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E2">
         <v>25</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="I2" s="2">
         <v>8.4</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K2" s="1">
-        <v>0</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1941,28 +1941,28 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E3">
         <v>25</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="I3" s="2">
         <v>8.4</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" s="1">
-        <v>0</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1991,7 +1991,7 @@
         <v>4.9</v>
       </c>
       <c r="I4" s="2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2014,19 +2014,19 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>91.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="I5" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2046,19 +2046,19 @@
         <v>75</v>
       </c>
       <c r="E6">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>93.3</v>
+        <v>94.7</v>
       </c>
       <c r="H6" s="1">
-        <v>6.7</v>
+        <v>5.3</v>
       </c>
       <c r="I6" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2192,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2212,28 +2212,28 @@
         <v>26</v>
       </c>
       <c r="D11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E11">
         <v>24</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>85.7</v>
+        <v>82.8</v>
       </c>
       <c r="H11" s="1">
-        <v>14.3</v>
+        <v>17.2</v>
       </c>
       <c r="I11" s="2">
         <v>7.6</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>0</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2244,28 +2244,28 @@
         <v>19</v>
       </c>
       <c r="D12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E12">
         <v>24</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" s="1">
-        <v>85.7</v>
+        <v>82.8</v>
       </c>
       <c r="H12" s="1">
-        <v>14.3</v>
+        <v>17.2</v>
       </c>
       <c r="I12" s="2">
         <v>7.6</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2279,28 +2279,28 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>45</v>
+        <v>76.2</v>
       </c>
       <c r="H13" s="1">
-        <v>55</v>
+        <v>23.8</v>
       </c>
       <c r="I13" s="2">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2384,28 +2384,28 @@
         <v>30</v>
       </c>
       <c r="D16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E16">
         <v>23</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I16" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2416,28 +2416,28 @@
         <v>19</v>
       </c>
       <c r="D17">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E17">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F17">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G17" s="1">
-        <v>76.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>23.6</v>
+        <v>17.6</v>
       </c>
       <c r="I17" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" s="1">
-        <v>0</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2451,28 +2451,28 @@
         <v>31</v>
       </c>
       <c r="D18">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E18">
         <v>40</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G18" s="1">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="I18" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K18" s="1">
-        <v>0</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2483,28 +2483,28 @@
         <v>19</v>
       </c>
       <c r="D19">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E19">
         <v>40</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G19" s="1">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="I19" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K19" s="1">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2512,28 +2512,28 @@
         <v>20</v>
       </c>
       <c r="D20">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E20">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F20">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G20" s="1">
-        <v>90.7</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>9.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="I20" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K20" s="1">
-        <v>0</v>
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Ciencias Sociales - Estadisticos 20241.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20241.xlsx
@@ -2317,19 +2317,19 @@
         <v>28</v>
       </c>
       <c r="E14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>75</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>25</v>
+        <v>17.9</v>
       </c>
       <c r="I14" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2352,19 +2352,19 @@
         <v>18</v>
       </c>
       <c r="E15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>4.2</v>
       </c>
       <c r="I16" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -2419,16 +2419,16 @@
         <v>91</v>
       </c>
       <c r="E17">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F17">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G17" s="1">
-        <v>82.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>17.6</v>
+        <v>12.1</v>
       </c>
       <c r="I17" s="2">
         <v>7</v>
@@ -2515,16 +2515,16 @@
         <v>335</v>
       </c>
       <c r="E20">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F20">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G20" s="1">
-        <v>90.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>9.9</v>
+        <v>8.4</v>
       </c>
       <c r="I20" s="2">
         <v>8</v>

--- a/academias/Ciencias Sociales - Estadisticos 20241.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20241.xlsx
@@ -534,25 +534,25 @@
         <v>29</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>79.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>20.7</v>
+        <v>6.9</v>
       </c>
       <c r="I2" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>13.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -566,25 +566,25 @@
         <v>29</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>79.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>20.7</v>
+        <v>6.9</v>
       </c>
       <c r="I3" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -837,25 +837,25 @@
         <v>29</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>82.8</v>
+        <v>86.2</v>
       </c>
       <c r="H11" s="1">
-        <v>17.2</v>
+        <v>13.8</v>
       </c>
       <c r="I11" s="2">
         <v>7.4</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -869,25 +869,25 @@
         <v>29</v>
       </c>
       <c r="E12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>82.8</v>
+        <v>86.2</v>
       </c>
       <c r="H12" s="1">
-        <v>17.2</v>
+        <v>13.8</v>
       </c>
       <c r="I12" s="2">
         <v>7.4</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -904,25 +904,25 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1">
-        <v>52.4</v>
+        <v>57.1</v>
       </c>
       <c r="H13" s="1">
-        <v>47.6</v>
+        <v>42.9</v>
       </c>
       <c r="I13" s="2">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1009,25 +1009,25 @@
         <v>24</v>
       </c>
       <c r="E16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="H16" s="1">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I16" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1041,25 +1041,25 @@
         <v>91</v>
       </c>
       <c r="E17">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F17">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G17" s="1">
-        <v>72.5</v>
+        <v>74.7</v>
       </c>
       <c r="H17" s="1">
-        <v>27.5</v>
+        <v>25.3</v>
       </c>
       <c r="I17" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>2.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1076,25 +1076,25 @@
         <v>44</v>
       </c>
       <c r="E18">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
         <v>9.1</v>
       </c>
-      <c r="I18" s="2">
-        <v>9</v>
-      </c>
       <c r="J18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1108,25 +1108,25 @@
         <v>44</v>
       </c>
       <c r="E19">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
         <v>9.1</v>
       </c>
-      <c r="I19" s="2">
-        <v>9</v>
-      </c>
       <c r="J19">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1137,25 +1137,25 @@
         <v>335</v>
       </c>
       <c r="E20">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="F20">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="G20" s="1">
-        <v>86.59999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>13.4</v>
+        <v>10.1</v>
       </c>
       <c r="I20" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J20">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1223,25 +1223,25 @@
         <v>29</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>13.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1255,25 +1255,25 @@
         <v>29</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1526,25 +1526,25 @@
         <v>29</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>82.8</v>
+        <v>86.2</v>
       </c>
       <c r="H11" s="1">
-        <v>17.2</v>
+        <v>13.8</v>
       </c>
       <c r="I11" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1558,25 +1558,25 @@
         <v>29</v>
       </c>
       <c r="E12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>82.8</v>
+        <v>86.2</v>
       </c>
       <c r="H12" s="1">
-        <v>17.2</v>
+        <v>13.8</v>
       </c>
       <c r="I12" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1593,25 +1593,25 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13" s="1">
-        <v>42.9</v>
+        <v>47.6</v>
       </c>
       <c r="H13" s="1">
-        <v>57.1</v>
+        <v>52.4</v>
       </c>
       <c r="I13" s="2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1698,25 +1698,25 @@
         <v>24</v>
       </c>
       <c r="E16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1730,25 +1730,25 @@
         <v>91</v>
       </c>
       <c r="E17">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F17">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G17" s="1">
-        <v>74.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>25.3</v>
+        <v>23.1</v>
       </c>
       <c r="I17" s="2">
         <v>7</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>2.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1765,25 +1765,25 @@
         <v>44</v>
       </c>
       <c r="E18">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1797,25 +1797,25 @@
         <v>44</v>
       </c>
       <c r="E19">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1826,25 +1826,25 @@
         <v>335</v>
       </c>
       <c r="E20">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="F20">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G20" s="1">
-        <v>88.09999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="H20" s="1">
-        <v>11.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I20" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J20">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1912,25 +1912,25 @@
         <v>29</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>13.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1944,25 +1944,25 @@
         <v>29</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>86.2</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>13.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1979,19 +1979,19 @@
         <v>41</v>
       </c>
       <c r="E4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>95.09999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="I4" s="2">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2014,19 +2014,19 @@
         <v>34</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>94.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="I5" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>75</v>
       </c>
       <c r="E6">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>94.7</v>
+        <v>97.3</v>
       </c>
       <c r="H6" s="1">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="I6" s="2">
         <v>8.6</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2125,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2215,25 +2215,25 @@
         <v>29</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>82.8</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>17.2</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2247,25 +2247,25 @@
         <v>29</v>
       </c>
       <c r="E12">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>82.8</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>17.2</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2282,25 +2282,25 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>76.2</v>
+        <v>81</v>
       </c>
       <c r="H13" s="1">
-        <v>23.8</v>
+        <v>19</v>
       </c>
       <c r="I13" s="2">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2387,25 +2387,25 @@
         <v>24</v>
       </c>
       <c r="E16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2419,25 +2419,25 @@
         <v>91</v>
       </c>
       <c r="E17">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F17">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G17" s="1">
-        <v>87.90000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>12.1</v>
+        <v>9.9</v>
       </c>
       <c r="I17" s="2">
         <v>7</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>2.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2454,25 +2454,25 @@
         <v>44</v>
       </c>
       <c r="E18">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2486,25 +2486,25 @@
         <v>44</v>
       </c>
       <c r="E19">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2515,25 +2515,25 @@
         <v>335</v>
       </c>
       <c r="E20">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="F20">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G20" s="1">
-        <v>91.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="H20" s="1">
-        <v>8.4</v>
+        <v>3.3</v>
       </c>
       <c r="I20" s="2">
         <v>8</v>
       </c>
       <c r="J20">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
